--- a/SGC-CKN/Excel/2c0f29d4-e284-498b-8db7-a61fb65a8eda_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-01_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/2c0f29d4-e284-498b-8db7-a61fb65a8eda_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-01_D800_20-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P11-01</t>
+    <t>P11-91</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/2c0f29d4-e284-498b-8db7-a61fb65a8eda_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-01_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/2c0f29d4-e284-498b-8db7-a61fb65a8eda_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-01_D800_20-03-2026.xlsx
@@ -1154,7 +1154,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G11" s="5">
         <v>-2.8</v>
@@ -1163,10 +1163,10 @@
         <v>0.17</v>
       </c>
       <c r="I11" s="5">
-        <v>1.59</v>
+        <v>4</v>
       </c>
       <c r="J11" s="8">
-        <v>9.54</v>
+        <v>24</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1367,16 +1367,16 @@
         <v>-38.2</v>
       </c>
       <c r="G17" s="24">
-        <v>-45.2</v>
+        <v>-45.3</v>
       </c>
       <c r="H17" s="24">
         <v>1.2</v>
       </c>
       <c r="I17" s="24">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J17" s="8">
-        <v>5.83</v>
+        <v>5.92</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>30</v>
@@ -1399,7 +1399,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="27">
-        <v>-45.2</v>
+        <v>-45.3</v>
       </c>
       <c r="G18" s="27">
         <v>-49.65</v>
@@ -1408,10 +1408,10 @@
         <v>5.08</v>
       </c>
       <c r="I18" s="27">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="J18" s="30">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="K18" s="28" t="s">
         <v>52</v>
@@ -1566,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.21</v>
+        <v>1.2</v>
       </c>
       <c r="F2" s="5">
         <v>-2.8</v>
@@ -1575,10 +1575,10 @@
         <v>0.17</v>
       </c>
       <c r="H2" s="5">
-        <v>1.59</v>
+        <v>4</v>
       </c>
       <c r="I2" s="8">
-        <v>9.54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1743,16 +1743,16 @@
         <v>-38.2</v>
       </c>
       <c r="F8" s="24">
-        <v>-45.2</v>
+        <v>-45.3</v>
       </c>
       <c r="G8" s="24">
         <v>1.2</v>
       </c>
       <c r="H8" s="24">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="I8" s="8">
-        <v>5.83</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="27">
-        <v>-45.2</v>
+        <v>-45.3</v>
       </c>
       <c r="F9" s="27">
         <v>-49.65</v>
@@ -1778,10 +1778,10 @@
         <v>5.08</v>
       </c>
       <c r="H9" s="27">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="I9" s="30">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1798,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-1.21</v>
+        <v>1.2</v>
       </c>
       <c r="F10" s="33">
         <v>-49.65</v>
@@ -1807,10 +1807,10 @@
         <v>9.7</v>
       </c>
       <c r="H10" s="33">
-        <v>48.44</v>
+        <v>50.85</v>
       </c>
       <c r="I10" s="33">
-        <v>4.99</v>
+        <v>5.24</v>
       </c>
     </row>
   </sheetData>
